--- a/public/sample-batch-import.xlsx
+++ b/public/sample-batch-import.xlsx
@@ -543,7 +543,7 @@
         <v>특이사항</v>
       </c>
       <c r="L1" t="str">
-        <v>복귀고려사항</v>
+        <v>특이사항메모</v>
       </c>
       <c r="M1" t="str">
         <v>진단코드</v>
